--- a/AAII_Financials/Quarterly/RDGA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RDGA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="92">
   <si>
     <t>RDGA</t>
   </si>
@@ -656,136 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -873,8 +880,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,8 +975,14 @@
       <c r="AE9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1051,8 +1070,14 @@
       <c r="AE10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1109,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1200,14 @@
       <c r="AE12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1295,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1351,8 +1390,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1485,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1521,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1559,8 +1612,14 @@
       <c r="AE17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,8 +1707,14 @@
       <c r="AE18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1746,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1770,8 +1837,14 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1859,8 +1932,14 @@
       <c r="AE21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1948,8 +2027,14 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2037,8 +2122,14 @@
       <c r="AE23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2217,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,8 +2312,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2304,8 +2407,14 @@
       <c r="AE26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2393,8 +2502,14 @@
       <c r="AE27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2692,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2882,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2838,8 +2977,14 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2927,8 +3072,14 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,8 +3167,14 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3105,102 +3262,114 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,8 +3436,10 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3354,8 +3527,14 @@
       <c r="AE41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3622,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3532,8 +3717,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3621,46 +3812,52 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
@@ -3674,11 +3871,11 @@
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="T45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3710,8 +3907,14 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3799,8 +4002,14 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,8 +4097,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3977,8 +4192,14 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4287,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4477,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4333,8 +4572,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,8 +4667,14 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -4511,8 +4762,14 @@
       <c r="AE54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4836,10 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4666,8 +4927,14 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4684,10 +4951,10 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4702,10 +4969,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>300</v>
@@ -4720,10 +4987,10 @@
         <v>300</v>
       </c>
       <c r="T58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V58" s="3">
         <v>200</v>
@@ -4744,10 +5011,10 @@
         <v>200</v>
       </c>
       <c r="AB58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD58" s="3">
         <v>100</v>
@@ -4755,8 +5022,14 @@
       <c r="AE58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4802,11 +5075,11 @@
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
@@ -4820,11 +5093,11 @@
       <c r="W59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="X59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4844,13 +5117,19 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
@@ -4862,10 +5141,10 @@
         <v>100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
@@ -4880,10 +5159,10 @@
         <v>0</v>
       </c>
       <c r="N60" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O60" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P60" s="3">
         <v>300</v>
@@ -4898,10 +5177,10 @@
         <v>300</v>
       </c>
       <c r="T60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V60" s="3">
         <v>200</v>
@@ -4922,10 +5201,10 @@
         <v>200</v>
       </c>
       <c r="AB60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD60" s="3">
         <v>100</v>
@@ -4933,8 +5212,14 @@
       <c r="AE60" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,8 +5307,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5111,8 +5402,14 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,13 +5687,19 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E66" s="3">
         <v>100</v>
@@ -5396,10 +5711,10 @@
         <v>100</v>
       </c>
       <c r="H66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J66" s="3">
         <v>0</v>
@@ -5414,10 +5729,10 @@
         <v>0</v>
       </c>
       <c r="N66" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O66" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P66" s="3">
         <v>300</v>
@@ -5432,10 +5747,10 @@
         <v>300</v>
       </c>
       <c r="T66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U66" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V66" s="3">
         <v>200</v>
@@ -5456,10 +5771,10 @@
         <v>200</v>
       </c>
       <c r="AB66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD66" s="3">
         <v>100</v>
@@ -5467,8 +5782,14 @@
       <c r="AE66" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,13 +6197,19 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="E72" s="3">
         <v>-2000</v>
@@ -5874,10 +6221,10 @@
         <v>-2000</v>
       </c>
       <c r="H72" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="I72" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="J72" s="3">
         <v>-1900</v>
@@ -5895,10 +6242,10 @@
         <v>-1900</v>
       </c>
       <c r="O72" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="P72" s="3">
-        <v>-1800</v>
+        <v>-1900</v>
       </c>
       <c r="Q72" s="3">
         <v>-1800</v>
@@ -5916,10 +6263,10 @@
         <v>-1800</v>
       </c>
       <c r="V72" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="W72" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="X72" s="3">
         <v>-1700</v>
@@ -5937,16 +6284,22 @@
         <v>-1700</v>
       </c>
       <c r="AC72" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AD72" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AE72" s="3">
         <v>-1600</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AG72" s="3">
+        <v>-1600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,8 +6577,14 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6227,10 +6598,10 @@
         <v>-100</v>
       </c>
       <c r="G76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I76" s="3">
         <v>0</v>
@@ -6248,10 +6619,10 @@
         <v>0</v>
       </c>
       <c r="N76" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="O76" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="P76" s="3">
         <v>-300</v>
@@ -6266,10 +6637,10 @@
         <v>-300</v>
       </c>
       <c r="T76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="U76" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="V76" s="3">
         <v>-200</v>
@@ -6290,10 +6661,10 @@
         <v>-200</v>
       </c>
       <c r="AB76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AC76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD76" s="3">
         <v>-100</v>
@@ -6301,8 +6672,14 @@
       <c r="AE76" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,102 +6767,114 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6573,8 +6962,14 @@
       <c r="AE81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7001,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6695,8 +7092,14 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7567,14 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7229,8 +7662,14 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7701,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7351,8 +7792,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7982,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7618,8 +8077,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8207,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8492,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8040,14 +8531,14 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -8096,8 +8587,14 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,8 +8682,14 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8272,6 +8775,12 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>
